--- a/X月新番首月评分.xlsx
+++ b/X月新番首月评分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\mzzbscore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F612244-0EC4-4391-B2FA-DFE91AA6D82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB98933-57BA-4743-B854-15D8A32BF44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3195" windowWidth="29040" windowHeight="15720" tabRatio="564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>2025年XX月新番X期评分（数据截止日期XXXX年XX月XX日）</t>
-  </si>
   <si>
     <t>原名</t>
   </si>
@@ -108,6 +105,10 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>2026年XX月新番X期评分（数据截止日期XXXX年XX月XX日）</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -864,7 +865,7 @@
   <sheetData>
     <row r="1" spans="1:916" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="65" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -876,78 +877,78 @@
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
       <c r="L1" s="7">
-        <v>20250714</v>
+        <v>20260410</v>
       </c>
     </row>
     <row r="2" spans="1:916" s="13" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="E2" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="F2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="G2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="H2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="I2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="J2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="K2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="L2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="61" t="s">
+      <c r="M2" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="N2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="O2" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="62" t="s">
+      <c r="P2" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="57" t="s">
+      <c r="Q2" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="57" t="s">
+      <c r="R2" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="57" t="s">
+      <c r="S2" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="57" t="s">
+      <c r="T2" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="57" t="s">
+      <c r="U2" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="V2" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="63" t="s">
+      <c r="W2" s="64" t="s">
         <v>22</v>
-      </c>
-      <c r="W2" s="64" t="s">
-        <v>23</v>
       </c>
       <c r="X2" s="12"/>
       <c r="Y2" s="12"/>
